--- a/Snapshot Metric.xlsx
+++ b/Snapshot Metric.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Purchase Price; Acquisition Price; Contract Price</t>
+          <t>Purchase Price; Acquisition Price; Contract Price; Asset Value; Gross Purchase Price; Land Cost; Site Cost; Acquisition Cost; Property Value; Purchase Value</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Closing Costs</t>
+          <t>Closing Costs; Transaction Costs; Acquisition Costs; Due Diligence Costs; Transfer Tax; Title Insurance; Legal Fees; Closing &amp; Transaction Costs; Soft Costs at Close</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Total Acquisition Cost / All-in Basis; All-in Basis; Total Basis; Acquisition Basis; Total Acquisition Cost</t>
+          <t>Total Acquisition Cost / All-in Basis; All-in Basis; Total Basis; Acquisition Basis; Total Acquisition Cost; Total Investment; Gross Investment; Total Capitalization</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Initial CapEx Budget; CapEx; Capital Expenditure; Capital Costs</t>
+          <t>Initial CapEx Budget; CapEx; Capital Expenditure; Capital Costs; Renovation Budget; Improvement Budget; Capital Improvements Budget; Capital Budget; CapEx Plan; Planned CapEx; Budgeted CapEx</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Total Project Cost; Total Development Cost; All-in Cost; Total All-in Cost; Total Cost</t>
+          <t>Total Project Cost; Total Development Cost; All-in Cost; Total All-in Cost; Total Cost; Total Uses; Total Project Budget; Gross Project Cost; Total Investment; Development Budget</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Debt Amount; Loan Proceeds; Initial Loan; Senior Loan; Initial Proceeds</t>
+          <t>Debt Amount; Loan Proceeds; Initial Loan; Senior Loan; Initial Proceeds; Loan Amount; Mortgage Amount; Senior Debt; Acquisition Loan; Loan Funding; Principal Amount; Funded Loan Amount</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Equity Invested; Total Equity; Equity Check; Equity; Total Equity Invested</t>
+          <t>Equity Invested; Total Equity; Equity Check; Equity; Total Equity Invested; Equity Contribution; Total Equity Contribution; Equity Commitment; Net Equity; Total Equity Required</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Going-in Cap Rate; Going-In Cap; Purchase Cap Rate; Acquisition Cap Rate</t>
+          <t>Going-in Cap Rate; Going-In Cap; Purchase Cap Rate; Acquisition Cap Rate; In-Place Cap Rate; T12 Cap Rate; Going-In Capitalization Rate; Initial Cap Rate</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Stabilized Yield on Cost; Yield on Cost (Stabilized); Stabilized YOC; Return on Cost; Untrended Return on Cost</t>
+          <t>Stabilized Yield on Cost; Yield on Cost (Stabilized); Stabilized YOC; Return on Cost; Untrended Return on Cost; Trended Return on Cost; Development Yield; Yield on Total Cost; Stabilized Return on Cost</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Potential Gross Revenue (PGR) / Potential Gross Income (PGI); Potential Gross Revenue; Potential Gross Income; PGR; PGI; Gross Potential Revenue; Gross Potential Income</t>
+          <t>Potential Gross Revenue (PGR) / Potential Gross Income (PGI); Potential Gross Revenue; Potential Gross Income; PGR; PGI; Gross Potential Revenue; Gross Potential Income; Gross Potential Rent; Scheduled Rent; Potential Rental Revenue; Scheduled Rental Revenue; GPR; Gross Rent; Market Rent Total; Gross Revenue; Total Scheduled Income</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Effective Gross Revenue / EGI; Effective Gross Revenue; Effective Gross Income; EGI; EGR</t>
+          <t>Effective Gross Revenue / EGI; Effective Gross Revenue; Effective Gross Income; EGI; EGR; Net Revenue; Total Revenue; Effective Revenue; Gross Revenue Net of Vacancy; Revenue After Vacancy; Adjusted Gross Revenue; Collected Revenue</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Operating Expenses; OpEx; Total Operating Expenses; Operating Expense</t>
+          <t>Operating Expenses; OpEx; Total Operating Expenses; Operating Expense; Total Expenses; Operating Costs; Total Operating Costs; G&amp;A; General &amp; Administrative; Property Operating Expenses; Operating &amp; Maintenance; Expenses Before Debt Service</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Net Operating Income (NOI); NOI; Net Operating Income; Net Income from Operations</t>
+          <t>Net Operating Income (NOI); NOI; Net Operating Income; Net Income from Operations; Annual NOI; Stabilized NOI; Net Property Income; Operating Net Income; Property NOI</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Debt Service; Annual Debt Service; Total Debt Service; Debt Service Payment</t>
+          <t>Debt Service; Annual Debt Service; Total Debt Service; Debt Service Payment; Mortgage Payment; Loan Payments; P&amp;I; Principal &amp; Interest; Interest &amp; Principal; Debt Service (Annual); Total Debt Payments</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Cash Flow After Debt Service; CFADS; Net Cash Flow After Debt; After-Debt Cash Flow</t>
+          <t>Cash Flow After Debt Service; CFADS; Net Cash Flow After Debt; After-Debt Cash Flow; Cash Flow to Equity; Net Cash Flow; Levered Cash Flow; Cash Available for Distribution; CAD; Distributable Cash Flow; Net Income After Debt</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Physical Occupancy; Occupancy Rate; Physical Occ; Occupancy %</t>
+          <t>Physical Occupancy; Occupancy Rate; Physical Occ; Occupancy %; Current Occupancy; Occupied %; Occupancy; Physical Occ %</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Original LTV; LTV; Loan to Value; Loan-to-Value</t>
+          <t>Original LTV; LTV; Loan to Value; Loan-to-Value; Initial LTV; Closing LTV; At-Close LTV; Acquisition LTV; Going-In LTV; LTV Ratio</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Debt Yield; DY</t>
+          <t>Debt Yield; DY; Net Operating Income / Loan; NOI / Loan Amount; Debt Yield Ratio; Loan Yield; Property Yield on Debt</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>DSCR / Debt Coverage Ratio; DSCR; Debt Service Coverage Ratio; Debt Coverage Ratio; Debt Coverage</t>
+          <t>DSCR / Debt Coverage Ratio; DSCR; Debt Service Coverage Ratio; Debt Coverage Ratio; Debt Coverage; Debt Service Coverage; Coverage Ratio; Debt Coverage Multiple</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Exit Value / Terminal Value; Exit Value; Terminal Value</t>
+          <t>Exit Value / Terminal Value; Exit Value; Terminal Value; Sale Value; Sale Price; Gross Sale Price; Disposition Value; Gross Proceeds; Reversion Value; Estimated Sale Price; Expected Sale Price; Property Value at Exit</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Levered IRR; IRR; IRR (Levered); Equity IRR; Project IRR</t>
+          <t>Levered IRR; IRR; Equity IRR; IRR (Levered); Project IRR; Deal IRR; Investment IRR; Leveraged IRR; Equity Return; Levered Return; Net IRR</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Equity Multiple; EM; Multiple</t>
+          <t>Equity Multiple; EM; Multiple; MOIC; Return Multiple; Equity Return Multiple; Cash-on-Cash Multiple; Total Return Multiple; Investment Multiple; Equity Multiple (x)</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Exit Cap Rate; Exit Cap; Cap Rate at Exit; Disposition Cap Rate; Sale Cap Rate; Terminal Cap Rate; Reversion Cap Rate</t>
+          <t>Exit Cap Rate; Exit Cap; Terminal Cap Rate; Reversion Cap Rate; Disposition Cap Rate; Sale Cap Rate; Cap Rate at Exit; Residual Cap Rate; Terminal Capitalization Rate; Exit Capitalization Rate</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Hold Period; Holding Period; Investment Period; Project Timeline; Total Project Timeline</t>
+          <t>Hold Period; Holding Period; Investment Period; Project Timeline; Total Project Timeline; Investment Horizon; Hold; Duration; Project Duration</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Total Units; Total # of Units; Number of Units; Unit Count; Total Unit Count</t>
+          <t>Total Units; Total # of Units; Number of Units; Unit Count; Total Unit Count; Residential Units; Apartment Units; # Apartments; Total Apartments; Units; Doors; Keys; Total Keys; Total Rooms; Total Beds; Keys / Rooms; Hotel Rooms</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Total SF; Total Gross SF; Gross SF; Total Square Feet; Gross Square Feet; Total GLA; Rentable SF; Total Rentable SF; NRA</t>
+          <t>Total SF; Total Gross SF; Gross SF; Total Square Feet; Gross Square Feet; Total GLA; Rentable SF; Total Rentable SF; NRA; Net Rentable Area; RSF; Rentable Square Feet; Total RSF; Leasable SF; GLA; Total NRA</t>
         </is>
       </c>
     </row>

--- a/Snapshot Metric.xlsx
+++ b/Snapshot Metric.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:Q104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,41 @@
           <t>formula</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>range_min</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>range_max</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>preferred_sheets</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>in_bounded_list</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -531,6 +566,35 @@
           <t>From PSA / closing statement</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>at_close</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>general info; investment summary; summary; sources &amp; uses; key uw</t>
+        </is>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -583,6 +647,25 @@
           <t>Sum of transaction costs</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -635,6 +718,25 @@
           <t>Purchase Price + Closing Costs + upfront CapEx + financing costs</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -687,6 +789,35 @@
           <t>Approved capex plan</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>capex; sources &amp; uses; budget; summary</t>
+        </is>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -739,6 +870,35 @@
           <t>Total Acquisition Cost + all future CapEx + TI/LC where relevant</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>at_close</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15000000000</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>sources &amp; uses; summary; general info; budget</t>
+        </is>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -791,6 +951,25 @@
           <t>From loan docs</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -843,6 +1022,25 @@
           <t>Total Project Cost - Debt Proceeds</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -895,6 +1093,25 @@
           <t>Total Basis ÷ NRA/GSF/Units/Keys</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -947,6 +1164,25 @@
           <t>Total Basis ÷ estimated replacement cost</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -999,6 +1235,35 @@
           <t>NOI at acquisition ÷ purchase price</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>at_close</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>key uw; summary; one pager</t>
+        </is>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1051,6 +1316,25 @@
           <t>Stabilized NOI ÷ total project cost</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1103,6 +1387,25 @@
           <t>Market Value - Total Basis</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1155,6 +1458,25 @@
           <t>Scheduled base rent + reimbursements + parking + misc income at full occupancy</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1207,6 +1529,25 @@
           <t>Market rent or scheduled rent on vacant units/spaces</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1259,6 +1600,25 @@
           <t>Write-offs or reserve assumption</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1311,6 +1671,25 @@
           <t>PGI - Vacancy - Credit Loss + other collected income</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1363,6 +1742,25 @@
           <t>Payroll + utilities + repairs + taxes + insurance + management fee + admin</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1415,6 +1813,25 @@
           <t>Tenant reimbursement calc per lease</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1467,6 +1884,35 @@
           <t>EGI - Operating Expenses</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>year_1</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>10000</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>key uw; summary; cash flow; proforma; one pager</t>
+        </is>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1519,6 +1965,25 @@
           <t>NOI ÷ EGI</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1571,6 +2036,25 @@
           <t>Sum of leasing-related costs in period</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1623,6 +2107,25 @@
           <t>CapEx paid in period</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1675,6 +2178,25 @@
           <t>Stabilized NOI - in-place NOI</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1727,6 +2249,25 @@
           <t>NOI - Leasing Costs - CapEx - reserves</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1779,6 +2320,25 @@
           <t>Per loan amortization / IO schedule</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1831,6 +2391,25 @@
           <t>NOI - leasing/capex reserve - debt service</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1883,6 +2462,25 @@
           <t>Cash flow after debt service - reserves - fund level obligations</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1935,6 +2533,25 @@
           <t>Current NOI - prior NOI; or % change</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1987,6 +2604,25 @@
           <t>Current stabilized comparable NOI vs prior period</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2039,6 +2675,35 @@
           <t>Occupied SF ÷ total leasable SF</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>at_close</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>general info; key uw; summary; one pager</t>
+        </is>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2091,6 +2756,25 @@
           <t>Collected / scheduled rent ÷ full market or scheduled rent</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2143,6 +2827,25 @@
           <t>Leased SF ÷ total leasable SF</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2195,6 +2898,25 @@
           <t>Vacant SF ÷ total leasable SF</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2247,6 +2969,25 @@
           <t>Σ(rent or area weight × remaining term) ÷ total weight</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2299,6 +3040,25 @@
           <t>Sum of expiring rent or area by year</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2351,6 +3111,25 @@
           <t>From rent roll</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2403,6 +3182,25 @@
           <t>Broker comps / market study</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2455,6 +3253,25 @@
           <t>Market Rent - In-place Rent</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2507,6 +3324,25 @@
           <t>(New Rent - prior/market rent) ÷ prior/market rent</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2559,6 +3395,25 @@
           <t>(Renewal Rent - prior rent) ÷ prior rent</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2611,6 +3466,25 @@
           <t>Total TI or LC ÷ leased SF</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2643,6 +3517,25 @@
           <t>mixed</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2695,6 +3588,25 @@
           <t>SF leased / month or units leased / month</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2747,6 +3659,25 @@
           <t>Months vacant between leases</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2799,6 +3730,25 @@
           <t>PV of rent net of free rent, TI, LC over term</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2851,6 +3801,25 @@
           <t>Renewed tenants ÷ expiring tenants</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2903,6 +3872,25 @@
           <t>Delinquent rent ÷ billed rent</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2955,6 +3943,25 @@
           <t>Tenant reported sales ÷ leased SF</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3007,6 +4014,25 @@
           <t>From business plan</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3059,6 +4085,25 @@
           <t>Cumulative paid invoices</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3111,6 +4156,25 @@
           <t>Actual - budget</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3163,6 +4227,25 @@
           <t>Budget - actual spent</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3215,6 +4298,25 @@
           <t>Updated project estimate</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3267,6 +4369,25 @@
           <t>Incremental NOI ÷ total capital deployed to date (incremental CapEx)</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3319,6 +4440,25 @@
           <t>Completed milestones ÷ total</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3371,6 +4511,25 @@
           <t>Current metric ÷ target metric</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3423,6 +4582,25 @@
           <t>Lease-up spend ÷ absorbed SF or units</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3475,6 +4653,25 @@
           <t>From amortization / servicing statement</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3527,6 +4724,35 @@
           <t>Original Loan ÷ value or cost</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>at_close</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>debt; debt information; key uw; summary</t>
+        </is>
+      </c>
+      <c r="Q60" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3579,6 +4805,25 @@
           <t>Current Loan Balance ÷ current value</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3631,6 +4876,25 @@
           <t>Loan Amount ÷ total project cost</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3683,6 +4947,35 @@
           <t>NOI ÷ current loan balance</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>year_1</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>debt; debt information; key uw</t>
+        </is>
+      </c>
+      <c r="Q63" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3735,6 +5028,35 @@
           <t>NOI or CFADS ÷ debt service</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>year_1</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O64" t="n">
+        <v>5</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>debt; debt information; key uw</t>
+        </is>
+      </c>
+      <c r="Q64" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3787,6 +5109,35 @@
           <t>Index + spread or fixed coupon</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>at_close</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>debt; debt information; key uw; summary</t>
+        </is>
+      </c>
+      <c r="Q65" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3839,6 +5190,25 @@
           <t>Based on amortization</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3891,6 +5261,35 @@
           <t>Loan docs / schedule</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>240</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>debt; debt information</t>
+        </is>
+      </c>
+      <c r="Q67" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3943,6 +5342,35 @@
           <t>Maturity date - today</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" t="n">
+        <v>600</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>debt; debt information</t>
+        </is>
+      </c>
+      <c r="Q68" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3995,6 +5423,25 @@
           <t>Forward NOI ÷ projected debt service</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4047,6 +5494,25 @@
           <t>(Opex + debt service - other income) ÷ potential gross income</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4099,6 +5565,25 @@
           <t>Actual metric - covenant threshold</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4151,6 +5636,25 @@
           <t>Compare actuals vs trigger levels</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4203,6 +5707,25 @@
           <t>From hedge schedule</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4255,6 +5778,25 @@
           <t>NOI ÷ market cap rate or DCF</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4307,6 +5849,25 @@
           <t>NOI ÷ cap rate</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4359,6 +5920,35 @@
           <t>Exit NOI ÷ exit cap rate - selling costs</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O76" t="n">
+        <v>50000000000</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>key uw; summary; one pager; returns</t>
+        </is>
+      </c>
+      <c r="Q76" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4411,6 +6001,35 @@
           <t>IRR on unlevered cash flows</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>key uw; returns; summary; one pager</t>
+        </is>
+      </c>
+      <c r="Q77" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4463,6 +6082,35 @@
           <t>IRR on equity cash flows</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>key uw; returns; summary; one pager</t>
+        </is>
+      </c>
+      <c r="Q78" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4515,6 +6163,35 @@
           <t>Total net distributions + sale proceeds ÷ equity invested</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>10</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>key uw; returns; summary; one pager</t>
+        </is>
+      </c>
+      <c r="Q79" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4567,6 +6244,25 @@
           <t>Cash flow after debt service ÷ average or beginning equity</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4619,6 +6315,25 @@
           <t>As above</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4671,6 +6386,25 @@
           <t>YOC - market cap</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4723,6 +6457,25 @@
           <t>Discount cash flows at required rate</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4775,6 +6528,25 @@
           <t>Market value - book basis</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4827,6 +6599,25 @@
           <t>Net proceeds - basis</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4879,6 +6670,25 @@
           <t>(Annual CF + (e.o. yr value - b.o. yr value))÷ e.o. year Value</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4931,6 +6741,25 @@
           <t>Break into NOI growth, cap rate change, leverage, timing</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4978,6 +6807,25 @@
           <t>LP Equity; LP Contribution; LP Capital; Limited Partner Equity; LP Equity Check</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5025,6 +6873,25 @@
           <t>GP Equity; Sponsor Equity; GP Contribution; Sponsor Contribution; General Partner Equity; GP Co-invest; Co-GP Equity</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5072,6 +6939,25 @@
           <t>Preferred Return; Pref Return; LP Preferred Return; Preferred Yield; Hurdle Rate; LP Hurdle; Pref</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5119,6 +7005,25 @@
           <t>GP Promote; Promote; Carried Interest; GP Carry; Carry; Promote Structure; Performance Fee</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5166,6 +7071,25 @@
           <t>LP/GP Split; LP / GP Split; Equity Split; Ownership Split; GP/LP Split; LP Ownership; GP Ownership</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5218,6 +7142,35 @@
           <t>Exit NOI / Exit Value</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>key uw; summary; one pager</t>
+        </is>
+      </c>
+      <c r="Q93" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5265,6 +7218,35 @@
           <t>Hold Period; Holding Period; Investment Period; Project Timeline; Total Project Timeline; Investment Horizon; Hold; Duration; Project Duration</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>1</v>
+      </c>
+      <c r="O94" t="n">
+        <v>20</v>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>general info; investment summary; summary; key uw</t>
+        </is>
+      </c>
+      <c r="Q94" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5312,6 +7294,35 @@
           <t>Total Units; Total # of Units; Number of Units; Unit Count; Total Unit Count; Residential Units; Apartment Units; # Apartments; Total Apartments; Doors; Keys; Total Keys; Total Rooms; Total Beds</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>stabilized</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>1</v>
+      </c>
+      <c r="O95" t="n">
+        <v>50000</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>general info; investment summary; one pager</t>
+        </is>
+      </c>
+      <c r="Q95" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5359,6 +7370,35 @@
           <t>Total SF; Total Gross SF; Gross SF; Total Square Feet; Gross Square Feet; Total GLA; Rentable SF; Total Rentable SF; NRA; Net Rentable Area; RSF; Rentable Square Feet; Total RSF; Leasable SF; GLA; Total NRA</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>sf</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>stabilized</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O96" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>general info; investment summary; one pager</t>
+        </is>
+      </c>
+      <c r="Q96" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5406,6 +7446,25 @@
           <t>Construction Loan; Senior Construction Loan; Construction Loan Proceeds; Construction Financing; Build Loan; Renovation Loan; Construction Facility</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5453,6 +7512,25 @@
           <t>Hard Costs; Total Hard Costs; Construction Costs; Direct Costs; Hard Cost Budget; GC Costs; Contractor Costs</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5499,6 +7577,387 @@
         <is>
           <t>Soft Costs; Total Soft Costs; Indirect Costs; Soft Cost Budget; A&amp;E Costs; Architecture &amp; Engineering; Professional Fees</t>
         </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Asset Name</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Investment Basis</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>The name of the asset / property / deal</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>General Information, Investment Summary</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>What is the deal?</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Asset Name; Investment Name; Deal Name; Property Name; Project Name</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>general info; investment summary; one pager; summary</t>
+        </is>
+      </c>
+      <c r="Q100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Property Type</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Investment Basis</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>The asset type — Hotel, Office, Multifamily, Industrial, Retail, etc.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>General Information, Investment Summary</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>What is the deal?</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Property Type; Asset Type; Property Class; Asset Class</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>general info; investment summary; one pager</t>
+        </is>
+      </c>
+      <c r="Q101" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Investment Basis</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>City, State or Submarket of the asset</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>General Information, Investment Summary</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>What is the deal?</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Location; Address; City, State; Market; Submarket; MSA; Geography</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>general info; investment summary; one pager</t>
+        </is>
+      </c>
+      <c r="Q102" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Parking Spaces</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Investment Basis</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Total number of parking spaces / stalls</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>General Information, Investment Summary</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>What is the deal?</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Parking Spaces; Parking Stalls; Total Parking; Parking Count; # Parking Spaces; Parking Ratio Source</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>100000</v>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>general info; investment summary</t>
+        </is>
+      </c>
+      <c r="Q103" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Exit NOI</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Valuation &amp; Returns</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Net Operating Income at sale / exit period</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Key UW Metrics, Cash Flow projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>What returns the deal targets?</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Exit NOI; Sale NOI; Terminal NOI; Forward NOI at Sale; Year of Sale NOI</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>10000</v>
+      </c>
+      <c r="O104" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>key uw; cash flow; summary</t>
+        </is>
+      </c>
+      <c r="Q104" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Snapshot Metric.xlsx
+++ b/Snapshot Metric.xlsx
@@ -885,7 +885,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Full cost to execute business plan</t>
+          <t>Total uses / all-in basis — the SUM of all sources or uses (acquisition + closing costs + CapEx + financing + reserves). Pick the TOTAL column of a sources/uses table, never the At-Close-only or per-unit column.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Total Project Cost; Total Development Cost; All-in Cost; Total All-in Cost; Total Cost</t>
+          <t>Total Project Cost; Total Uses; Total Sources; All-in Basis; All-in Cost; Total All-in Cost; Total Development Cost; Total Capitalization; Total Investment; Total Cost; Gross Project Cost; Total Project Budget</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">

--- a/Snapshot Metric.xlsx
+++ b/Snapshot Metric.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Planned improvement spend at acquisition</t>
+          <t>Total capital budget. Stabilized deals: planned CapEx / reserve. Value-add / development / conversion: the TOTAL construction budget (hard costs + soft costs + contingency). Pick the grand-total construction/capex figure — never a sub-line (hard-only, soft-only) or a per-unit/per-key value.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Initial CapEx Budget; CapEx Budget; Total CapEx; Total Capital Expenditure; CapEx; Capital Expenditure; Capital Costs; Renovation Cost; Renovation Budget; Total Renovation Cost; Capital Plan; Total Capital Plan; CapEx Total; Capital Improvement Budget; Total Capital Improvements</t>
+          <t>CapEx Budget; Total CapEx; Total Capital Expenditure; CapEx; Capital Expenditure; Renovation Budget; Total Renovation Cost; Construction Budget; Total Construction Cost; Total Construction Budget; Total Hard &amp; Soft Costs; Total Project Costs (excl. land); Capital Plan</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Total construction/renovation loan commitment (full draw amount, not just at-close funded)</t>
+          <t>Construction / development loan tranche. In conversion &amp; ground-up deals this funds the project and typically REPAYS the acquisition bridge loan; it is the operative total debt. Distinct from the initial acquisition loan (Debt Amount).</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Acquisition model, loan agreement</t>
+          <t>Debt, Sources &amp; Uses, Summary</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>What is the debt structure?</t>
+          <t>What is the construction/development debt?</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Construction Loan; Senior Construction Loan; Construction Loan Proceeds; Construction Financing; Build Loan; Renovation Loan; Construction Facility</t>
+          <t>Construction Loan; Construction Loan Proceeds; Senior Construction Loan; Construction Debt; Construction Facility; Senior Construction Lender; Development Loan; Construction Loan Funding</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7760,11 +7760,38 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>at_close</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O97" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>debt; sources &amp; uses; summary; inputs</t>
         </is>
       </c>
       <c r="Q97" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>leverage</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>debt; sources_uses; summary; inputs</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -8823,7 +8850,6 @@
           <t>Loan-to-Cost; LTC; Loan to Cost; Debt to Cost; Leverage (Cost)</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
           <t>ratio</t>
@@ -8853,7 +8879,6 @@
       <c r="Q110" t="b">
         <v>1</v>
       </c>
-      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
           <t>leverage</t>
